--- a/datasets/Dokazník_merged_association_rules_copy_copy.xlsx
+++ b/datasets/Dokazník_merged_association_rules_copy_copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniellieskovsky/Desktop/diplomova_praca/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B3AADE-6525-A34E-85D6-607A93336478}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1670DF12-A833-E14D-9DF8-DB9EC86D7A2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F04ECD9C-05C2-0645-B7E4-190B4FC26824}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F04ECD9C-05C2-0645-B7E4-190B4FC26824}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
